--- a/data/trans_bre/P57_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Clase-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 2,29</t>
+          <t>-7,41; 2,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,48</t>
+          <t>-6,87; 0,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 23,62</t>
+          <t>-46,61; 23,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 7,01</t>
+          <t>-50,35; 11,71</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 7,27</t>
+          <t>-2,97; 7,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 6,85</t>
+          <t>-1,17; 6,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 74,04</t>
+          <t>-21,04; 80,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 81,1</t>
+          <t>-11,02; 81,2</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 16,72</t>
+          <t>-0,18; 17,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 18,34</t>
+          <t>2,66; 20,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 80,13</t>
+          <t>-0,7; 84,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,67; 457,47</t>
+          <t>14,18; 400,7</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 5,38</t>
+          <t>-2,2; 5,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,2; -1,71</t>
+          <t>-11,45; -1,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 30,56</t>
+          <t>-10,86; 30,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,62; -12,72</t>
+          <t>-65,57; -10,91</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 9,32</t>
+          <t>-0,43; 9,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 7,61</t>
+          <t>-4,59; 7,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 37,43</t>
+          <t>-1,44; 37,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 43,88</t>
+          <t>-20,09; 43,82</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,84; 23,79</t>
+          <t>15,93; 23,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,83; 21,57</t>
+          <t>13,31; 21,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166,89; 629,15</t>
+          <t>175,05; 628,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166,87; 945,08</t>
+          <t>153,46; 923,78</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,1</t>
+          <t>3,2; 7,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,36</t>
+          <t>0,33; 6,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,94; 41,1</t>
+          <t>16,09; 39,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 59,86</t>
+          <t>3,65; 58,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-26,04%</t>
+          <t>-20,28%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 2,46</t>
+          <t>-7,01; 2,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,95</t>
+          <t>-6,37; 1,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 23,89</t>
+          <t>-45,97; 24,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 11,71</t>
+          <t>-45,66; 17,08</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 7,86</t>
+          <t>-2,85; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,54</t>
+          <t>-0,91; 6,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 80,2</t>
+          <t>-20,03; 81,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 81,2</t>
+          <t>-7,21; 87,5</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,59</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100,96%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 17,13</t>
+          <t>-0,41; 17,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 20,64</t>
+          <t>-1,54; 10,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 84,19</t>
+          <t>-1,43; 85,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,18; 400,7</t>
+          <t>-9,89; 81,87</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-2,24</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-36,5%</t>
+          <t>-15,39%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 5,33</t>
+          <t>-1,85; 5,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,45; -1,57</t>
+          <t>-5,19; 0,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 30,46</t>
+          <t>-9,38; 32,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,57; -10,91</t>
+          <t>-31,51; 4,09</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>6,29</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 9,31</t>
+          <t>-0,97; 9,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 7,61</t>
+          <t>2,03; 10,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 37,5</t>
+          <t>-3,18; 37,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 43,82</t>
+          <t>8,98; 63,72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18,04</t>
+          <t>16,76</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409,89%</t>
+          <t>319,87%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,93; 23,7</t>
+          <t>15,6; 23,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,31; 21,73</t>
+          <t>11,93; 20,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>175,05; 628,52</t>
+          <t>164,59; 643,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>153,46; 923,78</t>
+          <t>130,5; 724,5</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,08</t>
+          <t>2,79; 6,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,22</t>
+          <t>2,45; 5,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,09; 39,99</t>
+          <t>14,27; 39,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 58,8</t>
+          <t>16,92; 43,59</t>
         </is>
       </c>
     </row>
